--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
@@ -46,7 +46,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -73,7 +73,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -112,31 +112,31 @@
     <t>SI01</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée pathologies chroniques stabilisées (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Pathologies chroniques stabilisées (SI)</t>
   </si>
   <si>
     <t>SI02</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée oncologie et hémato-oncologie (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Oncologie et hémato-oncologie (SI)</t>
   </si>
   <si>
     <t>SI03</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée maladie rénale chronique (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Maladie rénale chronique, dialyse, transplantation rénale (SI)</t>
   </si>
   <si>
     <t>SI04</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée santé mentale (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Psychiatrie et santé mentale (SI)</t>
   </si>
   <si>
     <t>SI05</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée urgences (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Urgences (SI)</t>
   </si>
   <si>
     <t>SI06</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
@@ -46,7 +46,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260928120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -73,7 +73,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -628,7 +628,7 @@
     <t>SM76</t>
   </si>
   <si>
-    <t>Anesthésie-réanimation option anesthésie-pédiatrique (SM)</t>
+    <t>Anesthésie-réanimation option réanimation-pédiatrique (SM)</t>
   </si>
   <si>
     <t>SM77</t>
